--- a/code/data/combined/pelg+jmul-lcdm-fixed.xlsx
+++ b/code/data/combined/pelg+jmul-lcdm-fixed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,22 +467,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>543831.9299774526</v>
+        <v>543831.9299774516</v>
       </c>
       <c r="C2" t="n">
-        <v>-985857.6471269432</v>
+        <v>-985857.6471269405</v>
       </c>
       <c r="D2" t="n">
-        <v>74888.07319694814</v>
+        <v>74888.0731969467</v>
       </c>
       <c r="E2" t="n">
-        <v>221829.0705370424</v>
+        <v>221829.0705370425</v>
       </c>
       <c r="F2" t="n">
-        <v>-10062.16793666543</v>
+        <v>-10062.16793666472</v>
       </c>
       <c r="G2" t="n">
-        <v>-22067.40475038761</v>
+        <v>-22067.40475038759</v>
       </c>
     </row>
     <row r="3">
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-985857.6471270496</v>
+        <v>-985857.6471270471</v>
       </c>
       <c r="C3" t="n">
-        <v>2505464.025068827</v>
+        <v>2505464.025068821</v>
       </c>
       <c r="D3" t="n">
-        <v>-410464.0118388317</v>
+        <v>-410464.011838829</v>
       </c>
       <c r="E3" t="n">
-        <v>-423082.6601526329</v>
+        <v>-423082.6601526318</v>
       </c>
       <c r="F3" t="n">
-        <v>44839.0195306232</v>
+        <v>44839.01953062164</v>
       </c>
       <c r="G3" t="n">
-        <v>42500.3895462099</v>
+        <v>42500.38954620979</v>
       </c>
     </row>
     <row r="4">
@@ -517,22 +517,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74888.07319703528</v>
+        <v>74888.07319703442</v>
       </c>
       <c r="C4" t="n">
-        <v>-410464.0118389986</v>
+        <v>-410464.0118389964</v>
       </c>
       <c r="D4" t="n">
-        <v>285152.2969910082</v>
+        <v>285152.2969910073</v>
       </c>
       <c r="E4" t="n">
-        <v>48556.94444980272</v>
+        <v>48556.94444980228</v>
       </c>
       <c r="F4" t="n">
-        <v>-98803.12100753834</v>
+        <v>-98803.12100753785</v>
       </c>
       <c r="G4" t="n">
-        <v>-5392.025980883357</v>
+        <v>-5392.02598088332</v>
       </c>
     </row>
     <row r="5">
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>221829.0705370492</v>
+        <v>221829.0705370489</v>
       </c>
       <c r="C5" t="n">
-        <v>-423082.6601526013</v>
+        <v>-423082.6601526006</v>
       </c>
       <c r="D5" t="n">
-        <v>48556.94444976681</v>
+        <v>48556.94444976626</v>
       </c>
       <c r="E5" t="n">
-        <v>103838.2184716289</v>
+        <v>103838.2184716288</v>
       </c>
       <c r="F5" t="n">
-        <v>-17728.69561110154</v>
+        <v>-17728.69561110128</v>
       </c>
       <c r="G5" t="n">
-        <v>-10113.71201078401</v>
+        <v>-10113.71201078399</v>
       </c>
     </row>
     <row r="6">
@@ -567,22 +567,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-10062.16793669119</v>
+        <v>-10062.16793669099</v>
       </c>
       <c r="C6" t="n">
-        <v>44839.01953064688</v>
+        <v>44839.0195306464</v>
       </c>
       <c r="D6" t="n">
-        <v>-98803.12100751925</v>
+        <v>-98803.12100751883</v>
       </c>
       <c r="E6" t="n">
-        <v>-17728.69561111056</v>
+        <v>-17728.69561111051</v>
       </c>
       <c r="F6" t="n">
-        <v>82575.26717294895</v>
+        <v>82575.26717294878</v>
       </c>
       <c r="G6" t="n">
-        <v>3933.3863476398</v>
+        <v>3933.386347639791</v>
       </c>
     </row>
     <row r="7">
@@ -592,22 +592,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-22067.40475038802</v>
+        <v>-22067.40475038798</v>
       </c>
       <c r="C7" t="n">
-        <v>42500.38954620338</v>
+        <v>42500.38954620331</v>
       </c>
       <c r="D7" t="n">
-        <v>-5392.025980877578</v>
+        <v>-5392.025980877518</v>
       </c>
       <c r="E7" t="n">
-        <v>-10113.71201078368</v>
+        <v>-10113.71201078367</v>
       </c>
       <c r="F7" t="n">
-        <v>3933.38634763822</v>
+        <v>3933.386347638193</v>
       </c>
       <c r="G7" t="n">
-        <v>1160.792167775481</v>
+        <v>1160.79216777548</v>
       </c>
     </row>
   </sheetData>
